--- a/tests/testdata/excel/フォルダ/ファイル数が多い/ファイル028.xlsx
+++ b/tests/testdata/excel/フォルダ/ファイル数が多い/ファイル028.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E50A60E-45D5-4DCE-8980-A8D0E813F37D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{315CE3BD-F06F-4CB9-A97A-9865AEB901AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{A1B38DFB-3628-4468-8A0F-9EB762E3FD3B}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{19A705E3-11C4-4E44-87C8-5A5BCB8A58B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BFCD713-C4CE-41B4-BE96-E4EFD5B1D7EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04ECB6C8-6CB4-4C98-9A38-102D371E5CC0}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
